--- a/uploads/prueba.xlsx
+++ b/uploads/prueba.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
+  <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" tabRatio="600" firstSheet="0" activeTab="3" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -486,7 +486,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Hoja1">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -545,7 +545,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Hoja2">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -600,7 +600,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Hoja3">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -655,11 +655,11 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
+  <sheetPr codeName="Hoja4">
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:D9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,9 +692,6 @@
           <t>MTN923</t>
         </is>
       </c>
-      <c r="H3" t="n">
-        <v>3000</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -702,9 +699,6 @@
           <t>MTN277</t>
         </is>
       </c>
-      <c r="H4" t="n">
-        <v>2000</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -712,18 +706,12 @@
           <t>MTN802</t>
         </is>
       </c>
-      <c r="H5" t="n">
-        <v>789.2</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
           <t>MTN626</t>
         </is>
-      </c>
-      <c r="H6" t="n">
-        <v>2000</v>
       </c>
     </row>
     <row r="7"/>
@@ -732,9 +720,6 @@
         <is>
           <t>MTN833</t>
         </is>
-      </c>
-      <c r="H8" t="n">
-        <v>780</v>
       </c>
     </row>
     <row r="9">

--- a/uploads/prueba.xlsx
+++ b/uploads/prueba.xlsx
@@ -659,7 +659,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -692,6 +692,9 @@
           <t>MTN923</t>
         </is>
       </c>
+      <c r="G3" t="n">
+        <v>2542</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -720,6 +723,9 @@
         <is>
           <t>MTN833</t>
         </is>
+      </c>
+      <c r="G8" t="n">
+        <v>40</v>
       </c>
     </row>
     <row r="9">
